--- a/data/ui_tests.xlsx
+++ b/data/ui_tests.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -664,6 +664,425 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Verify homepage title</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>http://localhost:8012/</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2025-11-07 23:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Verify homepage title</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>http://localhost:8012/</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2025-11-07 23:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Verify homepage title</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>HTTP://LOCALHOST:8012/</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2025-11-07 23:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Verify homepage title</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>http://localhost:8012/</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2025-11-07 23:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Verify homepage title</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>http://localhost:8012/</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2025-11-07 23:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Verify homepage title</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>HTTP://LOCALHOST:8012/</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2025-11-07 23:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Verify homepage title</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>http://localhost:8012/</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2025-11-07 23:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Verify homepage title</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>http://localhost:8012/</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2025-11-07 23:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Verify homepage title</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>HTTP://LOCALHOST:8012/</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2025-11-07 23:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Verify homepage title</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>http://localhost:8012/</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2025-11-07 23:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Verify homepage title</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>http://localhost:8012/</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2025-11-07 23:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Verify homepage title</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>HTTP://LOCALHOST:8012/</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2025-11-07 23:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Verify homepage title</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>http://localhost:8012/</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2025-11-07 23:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Verify homepage title</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>http://localhost:8012/</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2025-11-07 23:52</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Verify homepage title</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>HTTP://LOCALHOST:8012/</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2025-11-07 23:52</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/ui_tests.xlsx
+++ b/data/ui_tests.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1031,12 +1031,6 @@
           <t>http://localhost:8012/</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>active</t>
@@ -1047,7 +1041,6 @@
           <t>2025-11-07 23:52</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1065,12 +1058,6 @@
           <t>HTTP://LOCALHOST:8012/</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>active</t>
@@ -1081,7 +1068,94 @@
           <t>2025-11-07 23:52</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Verify header logo</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>http://localhost:8012/</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2025-11-08 12:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Verify header logo</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>http://localhost:8012/</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2025-11-08 21:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Verify header logo</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>http://localhost:8012/</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2025-11-08 21:33</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
